--- a/WIP/工作簿222.xlsx
+++ b/WIP/工作簿222.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="法国" sheetId="1" r:id="rId1"/>
+    <sheet name="德国" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -442,11 +443,57 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="ID_8BE45564F174476EB008DF96A41A0EA6" descr="Portrait_PLS_Friedrich_IV"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1981200" cy="2667000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="ID_125BAE01ADED4FB19EAE7E7A165B5877" descr="Portrait_PLS_Gustav_Stresemann"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1981200" cy="2667000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="52">
   <si>
     <t>法兰西共和国</t>
   </si>
@@ -590,6 +637,18 @@
   </si>
   <si>
     <t>中央政治局</t>
+  </si>
+  <si>
+    <t>普鲁士王国</t>
+  </si>
+  <si>
+    <t>国王</t>
+  </si>
+  <si>
+    <t>腓特烈三世</t>
+  </si>
+  <si>
+    <t>古斯塔夫·施特雷泽曼</t>
   </si>
 </sst>
 </file>
@@ -2503,4 +2562,707 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A7:V37"/>
+  <sheetFormatPr defaultColWidth="22.7777777777778" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="16384" width="22.7777777777778" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="7:8">
+      <c r="G7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="7:8">
+      <c r="G8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="165" spans="7:8">
+      <c r="G9" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</f>
+        <v>=DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</v>
+      </c>
+      <c r="H9" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_125BAE01ADED4FB19EAE7E7A165B5877",1)</f>
+        <v>=DISPIMG("ID_125BAE01ADED4FB19EAE7E7A165B5877",1)</v>
+      </c>
+    </row>
+    <row r="10" spans="7:8">
+      <c r="G10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="7:7">
+      <c r="G11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="7:7">
+      <c r="G12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="5:21">
+      <c r="E13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="5:21">
+      <c r="E14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="5:22">
+      <c r="E15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="5:22">
+      <c r="E16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="M16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="Q16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2"/>
+      <c r="U16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2"/>
+    </row>
+    <row r="17" spans="5:22">
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="165" customHeight="1" spans="9:22">
+      <c r="I18" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</f>
+        <v>=DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</v>
+      </c>
+      <c r="J18" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+      <c r="M18" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</f>
+        <v>=DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</v>
+      </c>
+      <c r="N18" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+      <c r="Q18" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
+        <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
+      </c>
+      <c r="R18" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+      <c r="U18" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
+        <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
+      </c>
+      <c r="V18" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+    </row>
+    <row r="19" spans="5:22">
+      <c r="E19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="5:21">
+      <c r="E20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="5:21">
+      <c r="E21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="Q23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="Q24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="E25" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="J25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25"/>
+      <c r="Q25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R25" s="2"/>
+      <c r="U25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V25" s="2"/>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26"/>
+      <c r="Q26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" ht="165" customHeight="1" spans="1:22">
+      <c r="A27" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</f>
+        <v>=DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</v>
+      </c>
+      <c r="B27" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_4C649090737444C8B31291791A386581",1)</f>
+        <v>=DISPIMG("ID_4C649090737444C8B31291791A386581",1)</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</f>
+        <v>=DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</v>
+      </c>
+      <c r="F27" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</f>
+        <v>=DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</v>
+      </c>
+      <c r="J27" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</f>
+        <v>=DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</v>
+      </c>
+      <c r="K27" s="6" t="str">
+        <f>_xlfn.DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</f>
+        <v>=DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</v>
+      </c>
+      <c r="L27" s="6" t="str">
+        <f>_xlfn.DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</f>
+        <v>=DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</v>
+      </c>
+      <c r="M27" s="6" t="str">
+        <f>_xlfn.DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</f>
+        <v>=DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</v>
+      </c>
+      <c r="N27"/>
+      <c r="Q27" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</f>
+        <v>=DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</v>
+      </c>
+      <c r="R27" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
+        <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
+      </c>
+      <c r="U27" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
+        <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
+      </c>
+      <c r="V27" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
+        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
+      <c r="A28" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N28"/>
+      <c r="Q28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="U28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V28" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="E34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" ht="165" customHeight="1" spans="1:6">
+      <c r="A36" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_C36AB9415F9542E8BD8C857F58BE097C",1)</f>
+        <v>=DISPIMG("ID_C36AB9415F9542E8BD8C857F58BE097C",1)</v>
+      </c>
+      <c r="B36" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
+        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
+      </c>
+      <c r="E36" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_98A9663B5D6B40499B74B5F07BEE920D",1)</f>
+        <v>=DISPIMG("ID_98A9663B5D6B40499B74B5F07BEE920D",1)</v>
+      </c>
+      <c r="F36" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
+        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="E34:F34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/WIP/工作簿222.xlsx
+++ b/WIP/工作簿222.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="法国" sheetId="1" r:id="rId1"/>
-    <sheet name="德国" sheetId="2" r:id="rId2"/>
+    <sheet name="普鲁士" sheetId="2" r:id="rId2"/>
+    <sheet name="普鲁士国策" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -489,11 +490,34 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="ID_9B5E25B467354840860B770A994B94D9" descr="Portrait_FRA_Andre_Leon_Blum"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1981200" cy="2667000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="56">
   <si>
     <t>法兰西共和国</t>
   </si>
@@ -531,81 +555,84 @@
     <t>火十字党胜利</t>
   </si>
   <si>
+    <t>莱昂·布鲁姆</t>
+  </si>
+  <si>
+    <t>卡米耶·肖当</t>
+  </si>
+  <si>
+    <t>皮埃尔-埃蒂安·弗朗丹</t>
+  </si>
+  <si>
+    <t>弗朗索瓦·德·拉·罗克</t>
+  </si>
+  <si>
+    <t>保罗·诺斯</t>
+  </si>
+  <si>
+    <t>革命之火</t>
+  </si>
+  <si>
+    <t>两党合作</t>
+  </si>
+  <si>
+    <t>迎回波拿巴派</t>
+  </si>
+  <si>
+    <t>巩固独裁政权</t>
+  </si>
+  <si>
+    <t>法兰西公社</t>
+  </si>
+  <si>
+    <t>1939年总统候选人（部分）</t>
+  </si>
+  <si>
+    <t>法兰西帝国</t>
+  </si>
+  <si>
+    <t>法兰西国</t>
+  </si>
+  <si>
+    <t>主席</t>
+  </si>
+  <si>
+    <t>国防委员</t>
+  </si>
+  <si>
+    <t>革新主义</t>
+  </si>
+  <si>
+    <t>社会自由主义</t>
+  </si>
+  <si>
+    <t>保守民主主义</t>
+  </si>
+  <si>
+    <t>威权民主主义</t>
+  </si>
+  <si>
+    <t>皇帝</t>
+  </si>
+  <si>
+    <t>首相</t>
+  </si>
+  <si>
+    <t>执政官</t>
+  </si>
+  <si>
+    <t>行政机构</t>
+  </si>
+  <si>
+    <t>尼赫里·戴亚</t>
+  </si>
+  <si>
+    <t>阿尔弗雷德·格雷森特</t>
+  </si>
+  <si>
     <t>保罗·富勒</t>
   </si>
   <si>
-    <t>卡米耶·肖当</t>
-  </si>
-  <si>
-    <t>皮埃尔-埃蒂安·弗朗丹</t>
-  </si>
-  <si>
-    <t>弗朗索瓦·德·拉·罗克</t>
-  </si>
-  <si>
-    <t>保罗·诺斯</t>
-  </si>
-  <si>
-    <t>革命之火</t>
-  </si>
-  <si>
-    <t>两党合作</t>
-  </si>
-  <si>
-    <t>迎回波拿巴派</t>
-  </si>
-  <si>
-    <t>巩固独裁政权</t>
-  </si>
-  <si>
-    <t>法兰西公社</t>
-  </si>
-  <si>
-    <t>1939年总统候选人（部分）</t>
-  </si>
-  <si>
-    <t>法兰西帝国</t>
-  </si>
-  <si>
-    <t>法兰西国</t>
-  </si>
-  <si>
-    <t>主席</t>
-  </si>
-  <si>
-    <t>国防委员</t>
-  </si>
-  <si>
-    <t>革新主义</t>
-  </si>
-  <si>
-    <t>社会自由主义</t>
-  </si>
-  <si>
-    <t>保守民主主义</t>
-  </si>
-  <si>
-    <t>威权民主主义</t>
-  </si>
-  <si>
-    <t>皇帝</t>
-  </si>
-  <si>
-    <t>首相</t>
-  </si>
-  <si>
-    <t>执政官</t>
-  </si>
-  <si>
-    <t>行政机构</t>
-  </si>
-  <si>
-    <t>尼赫里·戴亚</t>
-  </si>
-  <si>
-    <t>阿尔弗雷德·格雷森特</t>
-  </si>
-  <si>
     <t>莱昂·儒奥</t>
   </si>
   <si>
@@ -627,18 +654,18 @@
     <t>国民议会</t>
   </si>
   <si>
+    <t>联盟选举-总工会胜出</t>
+  </si>
+  <si>
     <t>联盟选举-共产党胜出</t>
   </si>
   <si>
-    <t>联盟选举-总工会胜出</t>
+    <t>中央政治局</t>
   </si>
   <si>
     <t>莫里斯·多列士</t>
   </si>
   <si>
-    <t>中央政治局</t>
-  </si>
-  <si>
     <t>普鲁士王国</t>
   </si>
   <si>
@@ -649,6 +676,15 @@
   </si>
   <si>
     <t>古斯塔夫·施特雷泽曼</t>
+  </si>
+  <si>
+    <t>施特雷泽曼病逝</t>
+  </si>
+  <si>
+    <t>国王任命</t>
+  </si>
+  <si>
+    <t>最后的晚餐</t>
   </si>
 </sst>
 </file>
@@ -1309,9 +1345,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1856,690 +1895,1421 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="E7:AD37"/>
+  <sheetFormatPr defaultColWidth="22.7777777777778" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="8" width="22.7777777777778" style="2"/>
+    <col min="9" max="16384" width="22.7777777777778" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="15:16">
+      <c r="O7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3"/>
+    </row>
+    <row r="8" spans="15:16">
+      <c r="O8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="164.95" spans="15:16">
+      <c r="O9" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_493F53998CA04DB19D50C21913B05A8E",1)</f>
+        <v>=DISPIMG("ID_493F53998CA04DB19D50C21913B05A8E",1)</v>
+      </c>
+      <c r="P9" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+    </row>
+    <row r="10" spans="15:16">
+      <c r="O10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="15:15">
+      <c r="O11" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="15:15">
+      <c r="O12" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="13:29">
+      <c r="M13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="13:29">
+      <c r="M14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="13:30">
+      <c r="M15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="13:30">
+      <c r="M16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3"/>
+      <c r="Q16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="R16" s="3"/>
+      <c r="U16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="V16" s="3"/>
+      <c r="Y16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="3"/>
+      <c r="AC16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="13:30">
+      <c r="M17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="165" customHeight="1" spans="13:30">
+      <c r="M18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_9B5E25B467354840860B770A994B94D9",1)</f>
+        <v>=DISPIMG("ID_9B5E25B467354840860B770A994B94D9",1)</v>
+      </c>
+      <c r="N18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+      <c r="Q18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</f>
+        <v>=DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</v>
+      </c>
+      <c r="R18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+      <c r="U18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</f>
+        <v>=DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</v>
+      </c>
+      <c r="V18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+      <c r="Y18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
+        <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
+      </c>
+      <c r="Z18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+      <c r="AC18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
+        <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
+      </c>
+      <c r="AD18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+    </row>
+    <row r="19" spans="13:30">
+      <c r="M19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="U19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD19" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="13:29">
+      <c r="M20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="13:29">
+      <c r="M21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="9:29">
+      <c r="I22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="9:29">
+      <c r="I23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="Y23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC23" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="9:30">
+      <c r="I24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="Y24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="9:30">
+      <c r="I25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="M25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="R25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25"/>
+      <c r="Y25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z25" s="3"/>
+      <c r="AC25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD25" s="3"/>
+    </row>
+    <row r="26" spans="9:30">
+      <c r="I26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="R26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="S26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="V26"/>
+      <c r="Y26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD26" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" ht="165" customHeight="1" spans="9:30">
+      <c r="I27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</f>
+        <v>=DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</v>
+      </c>
+      <c r="J27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_4C649090737444C8B31291791A386581",1)</f>
+        <v>=DISPIMG("ID_4C649090737444C8B31291791A386581",1)</v>
+      </c>
+      <c r="M27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</f>
+        <v>=DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</v>
+      </c>
+      <c r="N27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</f>
+        <v>=DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</v>
+      </c>
+      <c r="R27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</f>
+        <v>=DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</v>
+      </c>
+      <c r="S27" s="7" t="str">
+        <f>_xlfn.DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</f>
+        <v>=DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</v>
+      </c>
+      <c r="T27" s="7" t="str">
+        <f>_xlfn.DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</f>
+        <v>=DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</v>
+      </c>
+      <c r="U27" s="7" t="str">
+        <f>_xlfn.DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</f>
+        <v>=DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</v>
+      </c>
+      <c r="V27"/>
+      <c r="Y27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</f>
+        <v>=DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</v>
+      </c>
+      <c r="Z27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
+        <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
+      </c>
+      <c r="AC27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
+        <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
+      </c>
+      <c r="AD27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
+        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
+      </c>
+    </row>
+    <row r="28" spans="9:30">
+      <c r="I28" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28" s="7"/>
+      <c r="M28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="R28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T28" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="V28"/>
+      <c r="Y28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD28" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="9:9">
+      <c r="I29" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="9:9">
+      <c r="I30" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="5:18">
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+    </row>
+    <row r="32" spans="5:18">
+      <c r="E32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+    </row>
+    <row r="33" spans="5:18">
+      <c r="E33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+    </row>
+    <row r="34" spans="5:18">
+      <c r="E34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="I34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="3"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+    </row>
+    <row r="35" spans="5:18">
+      <c r="E35" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+    </row>
+    <row r="36" ht="165" customHeight="1" spans="5:18">
+      <c r="E36" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_98A9663B5D6B40499B74B5F07BEE920D",1)</f>
+        <v>=DISPIMG("ID_98A9663B5D6B40499B74B5F07BEE920D",1)</v>
+      </c>
+      <c r="F36" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
+        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
+      </c>
+      <c r="I36" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_C36AB9415F9542E8BD8C857F58BE097C",1)</f>
+        <v>=DISPIMG("ID_C36AB9415F9542E8BD8C857F58BE097C",1)</v>
+      </c>
+      <c r="J36" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
+        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
+      </c>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+    </row>
+    <row r="37" spans="5:18">
+      <c r="E37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="Y16:Z16"/>
+    <mergeCell ref="AC16:AD16"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="R25:U25"/>
+    <mergeCell ref="Y25:Z25"/>
+    <mergeCell ref="AC25:AD25"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="I34:J34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A7:V37"/>
   <sheetFormatPr defaultColWidth="22.7777777777778" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="16384" width="22.7777777777778" style="1" customWidth="1"/>
+    <col min="1" max="16384" width="22.7777777777778" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="7" spans="7:8">
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="7:8">
+      <c r="G8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="165" spans="7:8">
+      <c r="G9" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</f>
+        <v>=DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</v>
+      </c>
+      <c r="H9" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_125BAE01ADED4FB19EAE7E7A165B5877",1)</f>
+        <v>=DISPIMG("ID_125BAE01ADED4FB19EAE7E7A165B5877",1)</v>
+      </c>
+    </row>
+    <row r="10" spans="7:8">
+      <c r="G10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="7:7">
+      <c r="G11" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="7:8">
+      <c r="G12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="5:21">
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="5:21">
+      <c r="E14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="5:22">
+      <c r="E15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="5:22">
+      <c r="E16" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="7:8">
-      <c r="G8" s="3" t="s">
+      <c r="F16" s="3"/>
+      <c r="I16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="M16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3"/>
+      <c r="Q16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="R16" s="3"/>
+      <c r="U16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="5:22">
+      <c r="E17" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="F17" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" ht="164.95" spans="7:8">
-      <c r="G9" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_493F53998CA04DB19D50C21913B05A8E",1)</f>
-        <v>=DISPIMG("ID_493F53998CA04DB19D50C21913B05A8E",1)</v>
-      </c>
-      <c r="H9" s="1" t="str">
+      <c r="I17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="165" customHeight="1" spans="9:22">
+      <c r="I18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</f>
+        <v>=DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</v>
+      </c>
+      <c r="J18" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
         <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
       </c>
-    </row>
-    <row r="10" spans="7:8">
-      <c r="G10" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="M18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</f>
+        <v>=DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</v>
+      </c>
+      <c r="N18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+      <c r="Q18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
+        <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
+      </c>
+      <c r="R18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+      <c r="U18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
+        <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
+      </c>
+      <c r="V18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
+        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+      </c>
+    </row>
+    <row r="19" spans="5:22">
+      <c r="E19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="7:7">
-      <c r="G11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="7:7">
-      <c r="G12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="5:21">
-      <c r="E13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="5:21">
-      <c r="E14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="5:22">
-      <c r="E15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="5:22">
-      <c r="E16" s="2" t="s">
+      <c r="I19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="U19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="V19" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="5:21">
+      <c r="E20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="5:21">
+      <c r="E21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="Q23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="Q24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="E25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="I16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2"/>
-      <c r="M16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="Q16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R16" s="2"/>
-      <c r="U16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2"/>
-    </row>
-    <row r="17" spans="5:22">
-      <c r="E17" s="3" t="s">
+      <c r="F25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25"/>
+      <c r="Q25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R25" s="3"/>
+      <c r="U25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V25" s="3"/>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" ht="165" customHeight="1" spans="5:22">
-      <c r="E18" s="1" t="str">
+      <c r="J26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26"/>
+      <c r="Q26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="V26" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" ht="165" customHeight="1" spans="1:22">
+      <c r="A27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</f>
+        <v>=DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</v>
+      </c>
+      <c r="B27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_4C649090737444C8B31291791A386581",1)</f>
+        <v>=DISPIMG("ID_4C649090737444C8B31291791A386581",1)</v>
+      </c>
+      <c r="E27" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</f>
         <v>=DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</v>
       </c>
-      <c r="F18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
-      <c r="I18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</f>
-        <v>=DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</v>
-      </c>
-      <c r="J18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
-      <c r="M18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</f>
-        <v>=DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</v>
-      </c>
-      <c r="N18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
-      <c r="Q18" s="1" t="str">
+      <c r="F27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</f>
+        <v>=DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</v>
+      </c>
+      <c r="J27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</f>
+        <v>=DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</v>
+      </c>
+      <c r="K27" s="7" t="str">
+        <f>_xlfn.DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</f>
+        <v>=DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</v>
+      </c>
+      <c r="L27" s="7" t="str">
+        <f>_xlfn.DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</f>
+        <v>=DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</v>
+      </c>
+      <c r="M27" s="7" t="str">
+        <f>_xlfn.DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</f>
+        <v>=DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</v>
+      </c>
+      <c r="N27"/>
+      <c r="Q27" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</f>
+        <v>=DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</v>
+      </c>
+      <c r="R27" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
         <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
       </c>
-      <c r="R18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
-      <c r="U18" s="1" t="str">
+      <c r="U27" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
         <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
       </c>
-      <c r="V18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
-    </row>
-    <row r="19" spans="5:22">
-      <c r="E19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="R19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="U19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="V19" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="5:21">
-      <c r="E20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="5:21">
-      <c r="E21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="A23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="Q23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
-      <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="Q24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
-      <c r="A25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="E25" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="J25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25"/>
-      <c r="Q25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R25" s="2"/>
-      <c r="U25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V25" s="2"/>
-    </row>
-    <row r="26" spans="1:22">
-      <c r="A26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N26"/>
-      <c r="Q26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" ht="165" customHeight="1" spans="1:22">
-      <c r="A27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</f>
-        <v>=DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</v>
-      </c>
-      <c r="B27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_4C649090737444C8B31291791A386581",1)</f>
-        <v>=DISPIMG("ID_4C649090737444C8B31291791A386581",1)</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</f>
-        <v>=DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</v>
-      </c>
-      <c r="F27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</f>
-        <v>=DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</v>
-      </c>
-      <c r="J27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</f>
-        <v>=DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</v>
-      </c>
-      <c r="K27" s="6" t="str">
-        <f>_xlfn.DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</f>
-        <v>=DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</v>
-      </c>
-      <c r="L27" s="6" t="str">
-        <f>_xlfn.DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</f>
-        <v>=DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</v>
-      </c>
-      <c r="M27" s="6" t="str">
-        <f>_xlfn.DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</f>
-        <v>=DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</v>
-      </c>
-      <c r="N27"/>
-      <c r="Q27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</f>
-        <v>=DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</v>
-      </c>
-      <c r="R27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
-        <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
-      </c>
-      <c r="U27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
-        <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
-      </c>
-      <c r="V27" s="1" t="str">
+      <c r="V27" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
         <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
       </c>
     </row>
     <row r="28" spans="1:22">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="4" t="s">
+      <c r="D28" s="7"/>
+      <c r="E28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="F28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="J28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="K28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M28" s="4" t="s">
+      <c r="L28" s="5" t="s">
         <v>41</v>
       </c>
+      <c r="M28" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="N28"/>
-      <c r="Q28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R28" s="4" t="s">
+      <c r="Q28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="R28" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="U28" s="4" t="s">
+      <c r="U28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="V28" s="4" t="s">
-        <v>43</v>
+      <c r="V28" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J31" s="1" t="s">
+      <c r="A31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="1" t="s">
+      <c r="A32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="5" t="s">
+      <c r="A33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="E34" s="2" t="s">
+      <c r="B34" s="3"/>
+      <c r="E34" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F34" s="2"/>
+      <c r="F34" s="3"/>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="36" ht="165" customHeight="1" spans="1:6">
-      <c r="A36" s="1" t="str">
+      <c r="A36" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_C36AB9415F9542E8BD8C857F58BE097C",1)</f>
         <v>=DISPIMG("ID_C36AB9415F9542E8BD8C857F58BE097C",1)</v>
       </c>
-      <c r="B36" s="1" t="str">
+      <c r="B36" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
         <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
       </c>
-      <c r="E36" s="1" t="str">
+      <c r="E36" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_98A9663B5D6B40499B74B5F07BEE920D",1)</f>
         <v>=DISPIMG("ID_98A9663B5D6B40499B74B5F07BEE920D",1)</v>
       </c>
-      <c r="F36" s="1" t="str">
+      <c r="F36" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
         <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="4" t="s">
+      <c r="A37" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" s="4" t="s">
+      <c r="E37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2564,704 +3334,45 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A7:V37"/>
-  <sheetFormatPr defaultColWidth="22.7777777777778" defaultRowHeight="15.6"/>
+  <dimension ref="E3:G6"/>
+  <sheetFormatPr defaultColWidth="20.7777777777778" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="16384" width="22.7777777777778" style="1" customWidth="1"/>
+    <col min="1" max="16384" width="20.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="7:8">
-      <c r="G7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="7:8">
-      <c r="G8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="165" spans="7:8">
-      <c r="G9" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</f>
-        <v>=DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</v>
-      </c>
-      <c r="H9" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_125BAE01ADED4FB19EAE7E7A165B5877",1)</f>
-        <v>=DISPIMG("ID_125BAE01ADED4FB19EAE7E7A165B5877",1)</v>
-      </c>
-    </row>
-    <row r="10" spans="7:8">
-      <c r="G10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="7:7">
-      <c r="G11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="7:7">
-      <c r="G12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="5:21">
-      <c r="E13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="5:21">
-      <c r="E14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="5:22">
-      <c r="E15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="5:22">
-      <c r="E16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="I16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2"/>
-      <c r="M16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="Q16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R16" s="2"/>
-      <c r="U16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2"/>
-    </row>
-    <row r="17" spans="5:22">
-      <c r="E17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" ht="165" customHeight="1" spans="9:22">
-      <c r="I18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</f>
-        <v>=DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</v>
-      </c>
-      <c r="J18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
-      <c r="M18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</f>
-        <v>=DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</v>
-      </c>
-      <c r="N18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
-      <c r="Q18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
-        <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
-      </c>
-      <c r="R18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
-      <c r="U18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
-        <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
-      </c>
-      <c r="V18" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
-    </row>
-    <row r="19" spans="5:22">
-      <c r="E19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="R19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="U19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="V19" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="5:21">
-      <c r="E20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="5:21">
-      <c r="E21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="A23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="Q23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
-      <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="Q24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
-      <c r="A25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="E25" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="J25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25"/>
-      <c r="Q25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R25" s="2"/>
-      <c r="U25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V25" s="2"/>
-    </row>
-    <row r="26" spans="1:22">
-      <c r="A26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N26"/>
-      <c r="Q26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" ht="165" customHeight="1" spans="1:22">
-      <c r="A27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</f>
-        <v>=DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</v>
-      </c>
-      <c r="B27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_4C649090737444C8B31291791A386581",1)</f>
-        <v>=DISPIMG("ID_4C649090737444C8B31291791A386581",1)</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</f>
-        <v>=DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</v>
-      </c>
-      <c r="F27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</f>
-        <v>=DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</v>
-      </c>
-      <c r="J27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</f>
-        <v>=DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</v>
-      </c>
-      <c r="K27" s="6" t="str">
-        <f>_xlfn.DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</f>
-        <v>=DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</v>
-      </c>
-      <c r="L27" s="6" t="str">
-        <f>_xlfn.DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</f>
-        <v>=DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</v>
-      </c>
-      <c r="M27" s="6" t="str">
-        <f>_xlfn.DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</f>
-        <v>=DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</v>
-      </c>
-      <c r="N27"/>
-      <c r="Q27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</f>
-        <v>=DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</v>
-      </c>
-      <c r="R27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
-        <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
-      </c>
-      <c r="U27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
-        <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
-      </c>
-      <c r="V27" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
-        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
-      <c r="A28" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="N28"/>
-      <c r="Q28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="U28" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="V28" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="E34" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" ht="165" customHeight="1" spans="1:6">
-      <c r="A36" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_C36AB9415F9542E8BD8C857F58BE097C",1)</f>
-        <v>=DISPIMG("ID_C36AB9415F9542E8BD8C857F58BE097C",1)</v>
-      </c>
-      <c r="B36" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
-        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
-      </c>
-      <c r="E36" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_98A9663B5D6B40499B74B5F07BEE920D",1)</f>
-        <v>=DISPIMG("ID_98A9663B5D6B40499B74B5F07BEE920D",1)</v>
-      </c>
-      <c r="F36" s="1" t="str">
-        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
-        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>47</v>
+    <row r="3" spans="7:7">
+      <c r="G3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="7:7">
+      <c r="G4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="5:7">
+      <c r="E5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="5:7">
+      <c r="E6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="E34:F34"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/WIP/工作簿222.xlsx
+++ b/WIP/工作簿222.xlsx
@@ -513,11 +513,34 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="ID_F56B23B77059461E90EA9E9FFA24906D" descr="Portrait_FRA_Julia_Bonaparte"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1981200" cy="2667000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="57">
   <si>
     <t>法兰西共和国</t>
   </si>
@@ -645,43 +668,46 @@
     <t>洛朗丝·让娜·特雷布</t>
   </si>
   <si>
+    <t>茱莉娅·波拿巴</t>
+  </si>
+  <si>
+    <t>拿破仑六世</t>
+  </si>
+  <si>
+    <t>国民议会</t>
+  </si>
+  <si>
+    <t>联盟选举-总工会胜出</t>
+  </si>
+  <si>
+    <t>联盟选举-共产党胜出</t>
+  </si>
+  <si>
+    <t>中央政治局</t>
+  </si>
+  <si>
+    <t>莫里斯·多列士</t>
+  </si>
+  <si>
+    <t>普鲁士王国</t>
+  </si>
+  <si>
+    <t>国王</t>
+  </si>
+  <si>
+    <t>腓特烈三世</t>
+  </si>
+  <si>
+    <t>古斯塔夫·施特雷泽曼</t>
+  </si>
+  <si>
+    <t>施特雷泽曼病逝</t>
+  </si>
+  <si>
+    <t>国王任命</t>
+  </si>
+  <si>
     <t>路易·波拿巴</t>
-  </si>
-  <si>
-    <t>拿破仑六世</t>
-  </si>
-  <si>
-    <t>国民议会</t>
-  </si>
-  <si>
-    <t>联盟选举-总工会胜出</t>
-  </si>
-  <si>
-    <t>联盟选举-共产党胜出</t>
-  </si>
-  <si>
-    <t>中央政治局</t>
-  </si>
-  <si>
-    <t>莫里斯·多列士</t>
-  </si>
-  <si>
-    <t>普鲁士王国</t>
-  </si>
-  <si>
-    <t>国王</t>
-  </si>
-  <si>
-    <t>腓特烈三世</t>
-  </si>
-  <si>
-    <t>古斯塔夫·施特雷泽曼</t>
-  </si>
-  <si>
-    <t>施特雷泽曼病逝</t>
-  </si>
-  <si>
-    <t>国王任命</t>
   </si>
   <si>
     <t>最后的晚餐</t>
@@ -2396,8 +2422,8 @@
         <v>=DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</v>
       </c>
       <c r="U27" s="7" t="str">
-        <f>_xlfn.DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</f>
-        <v>=DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</v>
+        <f>_xlfn.DISPIMG("ID_F56B23B77059461E90EA9E9FFA24906D",1)</f>
+        <v>=DISPIMG("ID_F56B23B77059461E90EA9E9FFA24906D",1)</v>
       </c>
       <c r="V27"/>
       <c r="Y27" s="2" t="str">
@@ -3171,7 +3197,7 @@
         <v>41</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="N28"/>
       <c r="Q28" s="5" t="s">
@@ -3345,7 +3371,7 @@
   <sheetData>
     <row r="3" spans="7:7">
       <c r="G3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="7:7">

--- a/WIP/工作簿222.xlsx
+++ b/WIP/工作簿222.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="法国" sheetId="1" r:id="rId1"/>
@@ -378,7 +378,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF" descr="Portrait_FRA_Louis_Bonaparte"/>
+        <xdr:cNvPr id="24" name="ID_30FB536F2FE2425299134B9A20D2FAC7" descr="Portrait_FRA_Francois_de_La_Rocque"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -401,7 +401,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="ID_30FB536F2FE2425299134B9A20D2FAC7" descr="Portrait_FRA_Francois_de_La_Rocque"/>
+        <xdr:cNvPr id="25" name="ID_AB0B89556D5548478122A7B84CBCEF59" descr="Portrait_FRA_Pierre-Etienne_Flandin"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -424,7 +424,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="ID_AB0B89556D5548478122A7B84CBCEF59" descr="Portrait_FRA_Pierre-Etienne_Flandin"/>
+        <xdr:cNvPr id="7" name="ID_8BE45564F174476EB008DF96A41A0EA6" descr="Portrait_PLS_Friedrich_IV"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -447,7 +447,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="ID_8BE45564F174476EB008DF96A41A0EA6" descr="Portrait_PLS_Friedrich_IV"/>
+        <xdr:cNvPr id="10" name="ID_125BAE01ADED4FB19EAE7E7A165B5877" descr="Portrait_PLS_Gustav_Stresemann"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -470,7 +470,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="ID_125BAE01ADED4FB19EAE7E7A165B5877" descr="Portrait_PLS_Gustav_Stresemann"/>
+        <xdr:cNvPr id="11" name="ID_9B5E25B467354840860B770A994B94D9" descr="Portrait_FRA_Andre_Leon_Blum"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -493,7 +493,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="ID_9B5E25B467354840860B770A994B94D9" descr="Portrait_FRA_Andre_Leon_Blum"/>
+        <xdr:cNvPr id="12" name="ID_F56B23B77059461E90EA9E9FFA24906D" descr="Portrait_FRA_Julia_Bonaparte"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -516,7 +516,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="ID_F56B23B77059461E90EA9E9FFA24906D" descr="Portrait_FRA_Julia_Bonaparte"/>
+        <xdr:cNvPr id="14" name="ID_367A62F57815475880B8BD1E42EA3676" descr="Portrait_PLS_Otto_Braun"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -536,11 +536,80 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="ID_FA210546E34D40228B9CCED858A584DA" descr="Portrait_PLS_Carl_Friedrich_Goerdeler"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1981200" cy="2667000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="ID_2950560720CA4F6180160EFDB082B895" descr="Portrait_PLS_Kurt_von_Schleicher"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1981200" cy="2667000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="ID_3E317931036D4185966B0D9BE06EA9FF" descr="Portrait_PLS_Hans_Luther"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1981200" cy="2667000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="64">
   <si>
     <t>法兰西共和国</t>
   </si>
@@ -704,13 +773,34 @@
     <t>施特雷泽曼病逝</t>
   </si>
   <si>
-    <t>国王任命</t>
-  </si>
-  <si>
-    <t>路易·波拿巴</t>
-  </si>
-  <si>
-    <t>最后的晚餐</t>
+    <t>继任决定神罗改革的命运</t>
+  </si>
+  <si>
+    <t>国王任命SPD首相</t>
+  </si>
+  <si>
+    <t>国王任命DVP首相</t>
+  </si>
+  <si>
+    <t>国王任命DZP首相</t>
+  </si>
+  <si>
+    <t>施莱歇尔弹劾成功</t>
+  </si>
+  <si>
+    <t>奥托·布劳恩</t>
+  </si>
+  <si>
+    <t>汉斯·路德</t>
+  </si>
+  <si>
+    <t>卡尔·格德勒</t>
+  </si>
+  <si>
+    <t>库尔特·冯·施莱歇尔</t>
+  </si>
+  <si>
+    <t>在神罗的最后一日</t>
   </si>
 </sst>
 </file>
@@ -2674,7 +2764,7 @@
         <v>50</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" ht="165" spans="7:8">
@@ -2700,15 +2790,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="7:8">
+    <row r="12" spans="7:9">
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="13" spans="5:21">
+      <c r="I12" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="5:22">
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
@@ -2754,14 +2847,11 @@
       <c r="S13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="T13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="5:21">
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+    </row>
+    <row r="14" spans="5:22">
       <c r="E14" s="2" t="s">
         <v>5</v>
       </c>
@@ -2774,163 +2864,156 @@
       <c r="Q14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
     </row>
     <row r="15" spans="5:22">
       <c r="E15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="6" t="s">
-        <v>11</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
     </row>
     <row r="16" spans="5:22">
       <c r="E16" s="3" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="N16" s="3"/>
       <c r="Q16" s="3" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R16" s="3"/>
-      <c r="U16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="V16" s="3"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
     </row>
     <row r="17" spans="5:22">
       <c r="E17" s="4" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="U17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V17" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" ht="165" customHeight="1" spans="9:22">
+        <v>32</v>
+      </c>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+    </row>
+    <row r="18" ht="165" customHeight="1" spans="5:22">
+      <c r="E18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</f>
+        <v>=DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_367A62F57815475880B8BD1E42EA3676",1)</f>
+        <v>=DISPIMG("ID_367A62F57815475880B8BD1E42EA3676",1)</v>
+      </c>
       <c r="I18" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</f>
-        <v>=DISPIMG("ID_7CF5E88BA5414CDFABA92E1768ADC3D6",1)</v>
+        <f>_xlfn.DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</f>
+        <v>=DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</v>
       </c>
       <c r="J18" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+        <f>_xlfn.DISPIMG("ID_3E317931036D4185966B0D9BE06EA9FF",1)</f>
+        <v>=DISPIMG("ID_3E317931036D4185966B0D9BE06EA9FF",1)</v>
       </c>
       <c r="M18" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</f>
-        <v>=DISPIMG("ID_AB0B89556D5548478122A7B84CBCEF59",1)</v>
+        <f>_xlfn.DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</f>
+        <v>=DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</v>
       </c>
       <c r="N18" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
+        <f>_xlfn.DISPIMG("ID_FA210546E34D40228B9CCED858A584DA",1)</f>
+        <v>=DISPIMG("ID_FA210546E34D40228B9CCED858A584DA",1)</v>
       </c>
       <c r="Q18" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
-        <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
+        <f>_xlfn.DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</f>
+        <v>=DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</v>
       </c>
       <c r="R18" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
-      <c r="U18" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
-        <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
-      </c>
-      <c r="V18" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</f>
-        <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
-      </c>
+        <f>_xlfn.DISPIMG("ID_2950560720CA4F6180160EFDB082B895",1)</f>
+        <v>=DISPIMG("ID_2950560720CA4F6180160EFDB082B895",1)</v>
+      </c>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
     </row>
     <row r="19" spans="5:22">
       <c r="E19" s="5" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="U19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="V19" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="5:21">
+        <v>62</v>
+      </c>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+    </row>
+    <row r="20" spans="5:22">
       <c r="E20" s="2" t="s">
         <v>5</v>
       </c>
@@ -2943,11 +3026,11 @@
       <c r="Q20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="U20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="5:21">
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+    </row>
+    <row r="21" spans="5:22">
       <c r="E21" s="2" t="s">
         <v>5</v>
       </c>
@@ -2960,400 +3043,358 @@
       <c r="Q21" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="A23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="Q23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+    </row>
+    <row r="22" spans="1:22">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+    </row>
+    <row r="23" spans="1:22">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
     </row>
     <row r="24" spans="1:22">
-      <c r="A24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="Q24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
+      <c r="R24"/>
+      <c r="T24"/>
+      <c r="U24"/>
+      <c r="V24"/>
     </row>
     <row r="25" spans="1:22">
-      <c r="A25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="E25" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="J25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
       <c r="N25"/>
-      <c r="Q25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R25" s="3"/>
-      <c r="U25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="V25" s="3"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+      <c r="R25"/>
+      <c r="T25"/>
+      <c r="U25"/>
+      <c r="V25"/>
     </row>
     <row r="26" spans="1:22">
-      <c r="A26" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
       <c r="N26"/>
-      <c r="Q26" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="V26" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="T26"/>
+      <c r="U26"/>
+      <c r="V26"/>
     </row>
     <row r="27" ht="165" customHeight="1" spans="1:22">
-      <c r="A27" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</f>
-        <v>=DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</v>
-      </c>
-      <c r="B27" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_4C649090737444C8B31291791A386581",1)</f>
-        <v>=DISPIMG("ID_4C649090737444C8B31291791A386581",1)</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</f>
-        <v>=DISPIMG("ID_5BB2E81A89B94589B748EBB70DF42231",1)</v>
-      </c>
-      <c r="F27" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</f>
-        <v>=DISPIMG("ID_F89AC77159E94345B652A1A4171B04D2",1)</v>
-      </c>
-      <c r="J27" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</f>
-        <v>=DISPIMG("ID_99B51661D8BC4FB5AC2339998EE596B9",1)</v>
-      </c>
-      <c r="K27" s="7" t="str">
-        <f>_xlfn.DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</f>
-        <v>=DISPIMG("ID_62CEDBB15FCE41B686E78FB92AE29A88",1)</v>
-      </c>
-      <c r="L27" s="7" t="str">
-        <f>_xlfn.DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</f>
-        <v>=DISPIMG("ID_BBD8047041E6437CA612318FDBCECE2B",1)</v>
-      </c>
-      <c r="M27" s="7" t="str">
-        <f>_xlfn.DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</f>
-        <v>=DISPIMG("ID_D01F21D8B2764EB7AEC65BF3E9C1B7DF",1)</v>
-      </c>
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
       <c r="N27"/>
-      <c r="Q27" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</f>
-        <v>=DISPIMG("ID_0B5697DFC5DF494F829679D6E7AD2B59",1)</v>
-      </c>
-      <c r="R27" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</f>
-        <v>=DISPIMG("ID_30FB536F2FE2425299134B9A20D2FAC7",1)</v>
-      </c>
-      <c r="U27" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</f>
-        <v>=DISPIMG("ID_6B42E2C0DF27440E81595390193C0D1C",1)</v>
-      </c>
-      <c r="V27" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
-        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
-      </c>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+      <c r="T27"/>
+      <c r="U27"/>
+      <c r="V27"/>
     </row>
     <row r="28" spans="1:22">
-      <c r="A28" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
       <c r="N28"/>
-      <c r="Q28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="U28" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="V28" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="E34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" ht="165" customHeight="1" spans="1:6">
-      <c r="A36" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_C36AB9415F9542E8BD8C857F58BE097C",1)</f>
-        <v>=DISPIMG("ID_C36AB9415F9542E8BD8C857F58BE097C",1)</v>
-      </c>
-      <c r="B36" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
-        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_98A9663B5D6B40499B74B5F07BEE920D",1)</f>
-        <v>=DISPIMG("ID_98A9663B5D6B40499B74B5F07BEE920D",1)</v>
-      </c>
-      <c r="F36" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</f>
-        <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>47</v>
-      </c>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+      <c r="T28"/>
+      <c r="U28"/>
+      <c r="V28"/>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+    </row>
+    <row r="36" ht="165" customHeight="1" spans="1:18">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="5">
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="M16:N16"/>
     <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="E34:F34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3371,7 +3412,7 @@
   <sheetData>
     <row r="3" spans="7:7">
       <c r="G3" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="7:7">

--- a/WIP/工作簿222.xlsx
+++ b/WIP/工作簿222.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="法国" sheetId="1" r:id="rId1"/>

--- a/WIP/工作簿222.xlsx
+++ b/WIP/工作簿222.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="法国" sheetId="1" r:id="rId1"/>
@@ -2012,10 +2012,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="E7:AD37"/>
-  <sheetFormatPr defaultColWidth="22.7777777777778" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="22.775" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="8" width="22.7777777777778" style="2"/>
-    <col min="9" max="16384" width="22.7777777777778" style="2" customWidth="1"/>
+    <col min="1" max="8" width="22.775" style="2"/>
+    <col min="9" max="16384" width="22.775" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="7" spans="15:16">
@@ -2748,9 +2748,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A7:V37"/>
-  <sheetFormatPr defaultColWidth="22.7777777777778" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="22.775" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="22.7777777777778" style="2" customWidth="1"/>
+    <col min="1" max="16384" width="22.775" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="7" spans="7:8">
@@ -3405,9 +3405,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="E3:G6"/>
-  <sheetFormatPr defaultColWidth="20.7777777777778" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="20.775" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="16384" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="1" max="16384" width="20.775" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="7:7">

--- a/WIP/工作簿222.xlsx
+++ b/WIP/工作簿222.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17655"/>
+    <workbookView windowWidth="27885" windowHeight="12375" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="法国" sheetId="1" r:id="rId1"/>
@@ -609,7 +609,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="86">
   <si>
     <t>法兰西共和国</t>
   </si>
@@ -800,7 +800,73 @@
     <t>库尔特·冯·施莱歇尔</t>
   </si>
   <si>
-    <t>在神罗的最后一日</t>
+    <t>前路漫漫……</t>
+  </si>
+  <si>
+    <t>（施特雷泽曼病逝）</t>
+  </si>
+  <si>
+    <t>……终有竟时</t>
+  </si>
+  <si>
+    <t>事件“在柏林的最后一日”</t>
+  </si>
+  <si>
+    <t>将军</t>
+  </si>
+  <si>
+    <t>&lt;-!-&gt;</t>
+  </si>
+  <si>
+    <t>最后机会</t>
+  </si>
+  <si>
+    <t>一线生机</t>
+  </si>
+  <si>
+    <t>广撒情报网</t>
+  </si>
+  <si>
+    <t>争取皇帝支持</t>
+  </si>
+  <si>
+    <t>民族浪潮</t>
+  </si>
+  <si>
+    <t>阴影之触</t>
+  </si>
+  <si>
+    <t>承诺安全保障</t>
+  </si>
+  <si>
+    <t>和平外交</t>
+  </si>
+  <si>
+    <t>潜伏的支持者们</t>
+  </si>
+  <si>
+    <t>抛出橄榄枝</t>
+  </si>
+  <si>
+    <t>统一的帝国铁路网络</t>
+  </si>
+  <si>
+    <t>巩固基本盘</t>
+  </si>
+  <si>
+    <t>重新商讨各邦国的地位</t>
+  </si>
+  <si>
+    <t>弃车保帅</t>
+  </si>
+  <si>
+    <t>工业支援</t>
+  </si>
+  <si>
+    <t>南德意志经济合作同盟</t>
+  </si>
+  <si>
+    <t>沉默的议案</t>
   </si>
 </sst>
 </file>
@@ -2018,13 +2084,13 @@
     <col min="9" max="16384" width="22.775" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="15:16">
+    <row r="7" spans="13:30">
       <c r="O7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="15:16">
+    <row r="8" spans="13:30">
       <c r="O8" s="4" t="s">
         <v>1</v>
       </c>
@@ -2032,7 +2098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" ht="164.95" spans="15:16">
+    <row r="9" ht="164.95" spans="13:30">
       <c r="O9" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_493F53998CA04DB19D50C21913B05A8E",1)</f>
         <v>=DISPIMG("ID_493F53998CA04DB19D50C21913B05A8E",1)</v>
@@ -2042,7 +2108,7 @@
         <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
       </c>
     </row>
-    <row r="10" spans="15:16">
+    <row r="10" spans="13:30">
       <c r="O10" s="5" t="s">
         <v>3</v>
       </c>
@@ -2050,17 +2116,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="15:15">
+    <row r="11" spans="13:30">
       <c r="O11" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="15:15">
+    <row r="12" spans="13:30">
       <c r="O12" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="13:29">
+    <row r="13" spans="13:30">
       <c r="M13" s="2" t="s">
         <v>6</v>
       </c>
@@ -2113,7 +2179,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="13:29">
+    <row r="14" spans="13:30">
       <c r="M14" s="2" t="s">
         <v>5</v>
       </c>
@@ -2184,7 +2250,7 @@
       </c>
       <c r="AD16" s="3"/>
     </row>
-    <row r="17" spans="13:30">
+    <row r="17" spans="5:30">
       <c r="M17" s="4" t="s">
         <v>1</v>
       </c>
@@ -2216,7 +2282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" ht="165" customHeight="1" spans="13:30">
+    <row r="18" ht="165" customHeight="1" spans="5:30">
       <c r="M18" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_9B5E25B467354840860B770A994B94D9",1)</f>
         <v>=DISPIMG("ID_9B5E25B467354840860B770A994B94D9",1)</v>
@@ -2258,7 +2324,7 @@
         <v>=DISPIMG("ID_B518E24FC4B44BDD8CE2A00C429D6F95",1)</v>
       </c>
     </row>
-    <row r="19" spans="13:30">
+    <row r="19" spans="5:30">
       <c r="M19" s="5" t="s">
         <v>12</v>
       </c>
@@ -2290,7 +2356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="13:29">
+    <row r="20" spans="5:30">
       <c r="M20" s="2" t="s">
         <v>5</v>
       </c>
@@ -2307,7 +2373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="13:29">
+    <row r="21" spans="5:30">
       <c r="M21" s="2" t="s">
         <v>5</v>
       </c>
@@ -2324,7 +2390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="9:29">
+    <row r="22" spans="5:30">
       <c r="I22" s="2" t="s">
         <v>6</v>
       </c>
@@ -2362,7 +2428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="9:29">
+    <row r="23" spans="5:30">
       <c r="I23" s="2" t="s">
         <v>5</v>
       </c>
@@ -2384,7 +2450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="9:30">
+    <row r="24" spans="5:30">
       <c r="I24" s="2" t="s">
         <v>5</v>
       </c>
@@ -2418,7 +2484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="9:30">
+    <row r="25" spans="5:30">
       <c r="I25" s="3" t="s">
         <v>21</v>
       </c>
@@ -2443,7 +2509,7 @@
       </c>
       <c r="AD25" s="3"/>
     </row>
-    <row r="26" spans="9:30">
+    <row r="26" spans="5:30">
       <c r="I26" s="4" t="s">
         <v>25</v>
       </c>
@@ -2482,7 +2548,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" ht="165" customHeight="1" spans="9:30">
+    <row r="27" ht="165" customHeight="1" spans="5:30">
       <c r="I27" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</f>
         <v>=DISPIMG("ID_A30A5F3F6621414284AC160534B321A3",1)</v>
@@ -2533,7 +2599,7 @@
         <v>=DISPIMG("ID_5DB37D32B60343BBB2A8FA65F262AFD8",1)</v>
       </c>
     </row>
-    <row r="28" spans="9:30">
+    <row r="28" spans="5:30">
       <c r="I28" s="5" t="s">
         <v>35</v>
       </c>
@@ -2573,17 +2639,17 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="9:9">
+    <row r="29" spans="5:30">
       <c r="I29" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="9:9">
+    <row r="30" spans="5:30">
       <c r="I30" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="5:18">
+    <row r="31" spans="5:30">
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
@@ -2609,7 +2675,7 @@
       <c r="Q31"/>
       <c r="R31"/>
     </row>
-    <row r="32" spans="5:18">
+    <row r="32" spans="5:30">
       <c r="E32" s="2" t="s">
         <v>5</v>
       </c>
@@ -2753,13 +2819,13 @@
     <col min="1" max="16384" width="22.775" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="7:8">
+    <row r="7" spans="5:22">
       <c r="G7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="7:8">
+    <row r="8" spans="5:22">
       <c r="G8" s="4" t="s">
         <v>50</v>
       </c>
@@ -2767,7 +2833,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" ht="165" spans="7:8">
+    <row r="9" ht="165" spans="5:22">
       <c r="G9" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</f>
         <v>=DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</v>
@@ -2777,7 +2843,7 @@
         <v>=DISPIMG("ID_125BAE01ADED4FB19EAE7E7A165B5877",1)</v>
       </c>
     </row>
-    <row r="10" spans="7:8">
+    <row r="10" spans="5:22">
       <c r="G10" s="5" t="s">
         <v>51</v>
       </c>
@@ -2785,12 +2851,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="7:7">
+    <row r="11" spans="5:22">
       <c r="G11" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="7:9">
+    <row r="12" spans="5:22">
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
@@ -2918,7 +2984,7 @@
       <c r="U16"/>
       <c r="V16"/>
     </row>
-    <row r="17" spans="5:22">
+    <row r="17" spans="1:22">
       <c r="E17" s="4" t="s">
         <v>50</v>
       </c>
@@ -2947,7 +3013,7 @@
       <c r="U17"/>
       <c r="V17"/>
     </row>
-    <row r="18" ht="165" customHeight="1" spans="5:22">
+    <row r="18" ht="165" customHeight="1" spans="1:22">
       <c r="E18" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</f>
         <v>=DISPIMG("ID_8BE45564F174476EB008DF96A41A0EA6",1)</v>
@@ -2984,7 +3050,7 @@
       <c r="U18"/>
       <c r="V18"/>
     </row>
-    <row r="19" spans="5:22">
+    <row r="19" spans="1:22">
       <c r="E19" s="5" t="s">
         <v>51</v>
       </c>
@@ -3013,7 +3079,7 @@
       <c r="U19"/>
       <c r="V19"/>
     </row>
-    <row r="20" spans="5:22">
+    <row r="20" spans="1:22">
       <c r="E20" s="2" t="s">
         <v>5</v>
       </c>
@@ -3030,7 +3096,7 @@
       <c r="U20"/>
       <c r="V20"/>
     </row>
-    <row r="21" spans="5:22">
+    <row r="21" spans="1:22">
       <c r="E21" s="2" t="s">
         <v>5</v>
       </c>
@@ -3208,7 +3274,7 @@
       <c r="U28"/>
       <c r="V28"/>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:22">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
@@ -3228,7 +3294,7 @@
       <c r="Q29"/>
       <c r="R29"/>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:22">
       <c r="A30"/>
       <c r="B30"/>
       <c r="C30"/>
@@ -3248,7 +3314,7 @@
       <c r="Q30"/>
       <c r="R30"/>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:22">
       <c r="A31"/>
       <c r="B31"/>
       <c r="C31"/>
@@ -3268,7 +3334,7 @@
       <c r="Q31"/>
       <c r="R31"/>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:22">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32"/>
@@ -3404,39 +3470,307 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="E3:G6"/>
-  <sheetFormatPr defaultColWidth="20.775" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="C3:R15"/>
+  <sheetFormatPr defaultColWidth="20.775" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="20.775" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="7:7">
-      <c r="G3" s="1" t="s">
+    <row r="3" spans="3:18">
+      <c r="K3" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="4" spans="7:7">
-      <c r="G4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="5:7">
-      <c r="E5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="5:7">
-      <c r="E6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>5</v>
+      <c r="L3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="3:18">
+      <c r="K4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="3:18">
+      <c r="H5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="3:18">
+      <c r="H6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="3:18">
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="3:18">
+      <c r="H8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="3:18">
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="3:18">
+      <c r="D10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="3:18">
+      <c r="D11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="3:18">
+      <c r="D12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="3:18">
+      <c r="C13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="3:18">
+      <c r="C14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="3:18">
+      <c r="C15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
